--- a/data/trans_orig/DC_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60154</t>
+          <t>61063</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57379</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79628</t>
+          <t>80956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96328</t>
+          <t>97116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130959</t>
+          <t>130274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251289</t>
+          <t>250380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277201</t>
+          <t>276924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210007</t>
+          <t>208679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232256</t>
+          <t>232179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470118</t>
+          <t>470803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>504749</t>
+          <t>503961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81369</t>
+          <t>81074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128176</t>
+          <t>125115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178281</t>
+          <t>179386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217651</t>
+          <t>217038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268447</t>
+          <t>267993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>331478</t>
+          <t>330867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390214</t>
+          <t>393275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437021</t>
+          <t>437316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297318</t>
+          <t>297931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336688</t>
+          <t>335583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701881</t>
+          <t>702492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>764912</t>
+          <t>765366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68890</t>
+          <t>70396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98825</t>
+          <t>100984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131490</t>
+          <t>133194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162295</t>
+          <t>163340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209623</t>
+          <t>210843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253578</t>
+          <t>253486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>217225</t>
+          <t>215066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>247160</t>
+          <t>245654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186833</t>
+          <t>185788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217638</t>
+          <t>215934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>411600</t>
+          <t>411692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>455555</t>
+          <t>454335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,3%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>46173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78174</t>
+          <t>76287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149705</t>
+          <t>152323</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312563</t>
+          <t>311597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204590</t>
+          <t>209763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>417719</t>
+          <t>403492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234383</t>
+          <t>236270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265536</t>
+          <t>266384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163155</t>
+          <t>164121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326013</t>
+          <t>323395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370555</t>
+          <t>384782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>583684</t>
+          <t>578511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43342</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101681</t>
+          <t>101412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74596</t>
+          <t>78737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132965</t>
+          <t>134016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135400</t>
+          <t>135034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151358</t>
+          <t>151812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157098</t>
+          <t>157367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217621</t>
+          <t>218738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304556</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>362925</t>
+          <t>358784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76246</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103128</t>
+          <t>104133</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107881</t>
+          <t>106313</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133548</t>
+          <t>132833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>189658</t>
+          <t>190746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>227592</t>
+          <t>226905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166508</t>
+          <t>165503</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193390</t>
+          <t>191617</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123508</t>
+          <t>124223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>149175</t>
+          <t>150743</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>299100</t>
+          <t>299787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337034</t>
+          <t>335946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173256</t>
+          <t>172664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229065</t>
+          <t>224633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>477762</t>
+          <t>475749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>703066</t>
+          <t>709549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>648520</t>
+          <t>648194</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1046057</t>
+          <t>1026626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>395214</t>
+          <t>399646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>451023</t>
+          <t>451615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146199</t>
+          <t>139716</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371503</t>
+          <t>373516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>427487</t>
+          <t>446918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>825024</t>
+          <t>825350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59942</t>
+          <t>61347</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191363</t>
+          <t>192401</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>221345</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266597</t>
+          <t>261896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>236883</t>
+          <t>228199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>453282</t>
+          <t>456229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>737357</t>
+          <t>736319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>868778</t>
+          <t>867373</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>451134</t>
+          <t>455835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>496386</t>
+          <t>496659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1193170</t>
+          <t>1190223</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1409569</t>
+          <t>1418253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>593275</t>
+          <t>570239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>826212</t>
+          <t>823821</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1469461</t>
+          <t>1468343</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2013722</t>
+          <t>2005111</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2139444</t>
+          <t>2157419</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2875621</t>
+          <t>2827859</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2633605</t>
+          <t>2635996</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2866542</t>
+          <t>2889578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1698558</t>
+          <t>1707169</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2242819</t>
+          <t>2243937</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4296476</t>
+          <t>4344238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5032653</t>
+          <t>5014678</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DC_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44934</t>
+          <t>46895</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67943</t>
+          <t>73689</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57456</t>
+          <t>62844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80956</t>
+          <t>85684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>112876</t>
+          <t>120584</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97116</t>
+          <t>105417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130274</t>
+          <t>138075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266509</t>
+          <t>271950</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250380</t>
+          <t>259106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>276924</t>
+          <t>283334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>221692</t>
+          <t>242372</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208679</t>
+          <t>230377</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232179</t>
+          <t>253217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>488201</t>
+          <t>514322</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470803</t>
+          <t>496831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>503961</t>
+          <t>529489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>101805</t>
+          <t>105642</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81074</t>
+          <t>85469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125115</t>
+          <t>128961</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>196903</t>
+          <t>206498</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179386</t>
+          <t>186314</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217038</t>
+          <t>228305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>298708</t>
+          <t>312140</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>267993</t>
+          <t>280616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>330867</t>
+          <t>341300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>416585</t>
+          <t>425005</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393275</t>
+          <t>401686</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437316</t>
+          <t>445178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>318066</t>
+          <t>339996</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297931</t>
+          <t>318189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335583</t>
+          <t>360180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>734651</t>
+          <t>765001</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702492</t>
+          <t>735841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765366</t>
+          <t>796525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83356</t>
+          <t>84418</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70396</t>
+          <t>71505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100984</t>
+          <t>100556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147084</t>
+          <t>152114</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133194</t>
+          <t>137148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163340</t>
+          <t>167390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>230440</t>
+          <t>236532</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210843</t>
+          <t>215074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253486</t>
+          <t>257273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>232694</t>
+          <t>231575</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215066</t>
+          <t>215437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245654</t>
+          <t>244488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>202044</t>
+          <t>204267</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185788</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215934</t>
+          <t>219233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>434738</t>
+          <t>435843</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>411692</t>
+          <t>415102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454335</t>
+          <t>457301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60441</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46173</t>
+          <t>48468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76287</t>
+          <t>83161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>207689</t>
+          <t>155130</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152323</t>
+          <t>138017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>311597</t>
+          <t>174027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>268129</t>
+          <t>219617</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209763</t>
+          <t>193823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403492</t>
+          <t>244915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>252116</t>
+          <t>308658</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236270</t>
+          <t>289984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266384</t>
+          <t>324677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>268029</t>
+          <t>266831</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164121</t>
+          <t>247934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323395</t>
+          <t>283944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>520145</t>
+          <t>575490</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384782</t>
+          <t>550192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578511</t>
+          <t>601284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>73946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101412</t>
+          <t>95546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>113741</t>
+          <t>122501</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78737</t>
+          <t>107822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134016</t>
+          <t>136482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>144243</t>
+          <t>167459</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135034</t>
+          <t>157264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151812</t>
+          <t>175572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>179537</t>
+          <t>144623</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157367</t>
+          <t>133372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218738</t>
+          <t>154972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>323780</t>
+          <t>312081</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>298100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358784</t>
+          <t>326760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>87961</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78019</t>
+          <t>75149</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104133</t>
+          <t>100673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>119239</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106313</t>
+          <t>109090</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>132833</t>
+          <t>134155</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>208827</t>
+          <t>209715</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190746</t>
+          <t>190957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226905</t>
+          <t>228384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>180048</t>
+          <t>182746</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165503</t>
+          <t>170034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191617</t>
+          <t>195558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>137817</t>
+          <t>141996</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124223</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150743</t>
+          <t>154660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>317865</t>
+          <t>324742</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>299787</t>
+          <t>306073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>335946</t>
+          <t>343500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,27%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>229516</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172664</t>
+          <t>200227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224633</t>
+          <t>256038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>573965</t>
+          <t>446649</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>475749</t>
+          <t>421156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>709549</t>
+          <t>473428</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>772427</t>
+          <t>676165</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>648194</t>
+          <t>635144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1026626</t>
+          <t>712445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>425817</t>
+          <t>490171</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>399646</t>
+          <t>463649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>451615</t>
+          <t>519460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>275300</t>
+          <t>325408</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139716</t>
+          <t>298629</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>373516</t>
+          <t>350901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>701117</t>
+          <t>815579</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>446918</t>
+          <t>779299</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>825350</t>
+          <t>856600</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>134512</t>
+          <t>152110</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61347</t>
+          <t>133090</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>192401</t>
+          <t>174324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>241686</t>
+          <t>275232</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>221072</t>
+          <t>253807</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261896</t>
+          <t>299561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>376198</t>
+          <t>427342</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>228199</t>
+          <t>397098</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>456229</t>
+          <t>459370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>794208</t>
+          <t>645962</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>736319</t>
+          <t>623748</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>867373</t>
+          <t>664982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>476045</t>
+          <t>556099</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>455835</t>
+          <t>531770</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>496659</t>
+          <t>577524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1270254</t>
+          <t>1202061</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1190223</t>
+          <t>1170033</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1418253</t>
+          <t>1232305</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>747597</t>
+          <t>809235</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>570239</t>
+          <t>759866</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>823821</t>
+          <t>864592</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1633750</t>
+          <t>1515362</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1468343</t>
+          <t>1464653</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2005111</t>
+          <t>1567010</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2381347</t>
+          <t>2324597</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2157419</t>
+          <t>2244812</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2827859</t>
+          <t>2402482</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2712220</t>
+          <t>2723527</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2635996</t>
+          <t>2668170</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2889578</t>
+          <t>2772896</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2078530</t>
+          <t>2221592</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1707169</t>
+          <t>2169944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2243937</t>
+          <t>2272301</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4790750</t>
+          <t>4945119</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4344238</t>
+          <t>4867234</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5014678</t>
+          <t>5024904</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
